--- a/public/templates/internal_upload_template.xlsx
+++ b/public/templates/internal_upload_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\timesheet-app\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4029CF-7E82-4C12-803C-30FEE15218F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EC4AA3-3184-4F03-A989-A03105AF82E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{013FBE18-F61B-431E-9C57-53EF7E3B5338}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{013FBE18-F61B-431E-9C57-53EF7E3B5338}"/>
   </bookViews>
   <sheets>
     <sheet name="Internal" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Email</t>
   </si>
@@ -75,15 +75,6 @@
     <t>DEV</t>
   </si>
   <si>
-    <t>DBA</t>
-  </si>
-  <si>
-    <t>PMO</t>
-  </si>
-  <si>
-    <t>ScrumMaster</t>
-  </si>
-  <si>
     <t>Bristol Bertha</t>
   </si>
   <si>
@@ -94,6 +85,48 @@
   </si>
   <si>
     <t>Rahil Shaikh</t>
+  </si>
+  <si>
+    <t>Delivery/Scrum Master</t>
+  </si>
+  <si>
+    <t>BSA</t>
+  </si>
+  <si>
+    <t>DTC</t>
+  </si>
+  <si>
+    <t>Release Management</t>
+  </si>
+  <si>
+    <t>MySlide</t>
+  </si>
+  <si>
+    <t>Data Engineer</t>
+  </si>
+  <si>
+    <t>Websites</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>Integrations</t>
+  </si>
+  <si>
+    <t>PolicyAttach</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>IT GRC</t>
+  </si>
+  <si>
+    <t>IT Ops</t>
   </si>
 </sst>
 </file>
@@ -124,12 +157,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -145,10 +184,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -508,10 +548,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
@@ -522,10 +562,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -588,17 +628,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0FA41776-A8B2-41D4-962D-58E40DD6F8EB}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB3F450A-A240-4E1D-B4E7-1822D4ED1215}">
           <x14:formula1>
-            <xm:f>data!$A$2:$A$5</xm:f>
+            <xm:f>data!$A$2:$A$21</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C1048576</xm:sqref>
+          <xm:sqref>C1:C1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A337F88A-649D-4D4A-B1A4-B345B60A9A35}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{027162DB-897E-4004-934A-43C934DD1121}">
           <x14:formula1>
-            <xm:f>data!$B$2:$B$7</xm:f>
+            <xm:f>data!$B$2:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
+          <xm:sqref>D1:D1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -608,128 +648,105 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43AA28A4-1708-49C1-9939-94064891E6E1}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2" t="str">
-        <f>"'"&amp;B2&amp;"'),"</f>
-        <v>'PMO'),</v>
-      </c>
-      <c r="H2" t="str">
-        <f>"("&amp;F2&amp;","&amp;G2</f>
-        <v>(4,'PMO'),</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3" t="str">
-        <f>"'"&amp;B3&amp;"'),"</f>
-        <v>'DEV'),</v>
-      </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H7" si="0">"("&amp;F3&amp;","&amp;G3</f>
-        <v>(4,'DEV'),</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4" t="str">
-        <f>"'"&amp;B4&amp;"'),"</f>
-        <v>'QA'),</v>
-      </c>
-      <c r="H4" t="str">
-        <f t="shared" si="0"/>
-        <v>(4,'QA'),</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" t="str">
-        <f>"'"&amp;B5&amp;"'),"</f>
-        <v>'BA'),</v>
-      </c>
-      <c r="H5" t="str">
-        <f t="shared" si="0"/>
-        <v>(4,'BA'),</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
       <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="str">
-        <f>"'"&amp;B6&amp;"'),"</f>
-        <v>'DBA'),</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>(4,'DBA'),</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
       <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7" t="str">
-        <f>"'"&amp;B7&amp;"'),"</f>
-        <v>'ScrumMaster'),</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" si="0"/>
-        <v>(4,'ScrumMaster'),</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/internal_upload_template.xlsx
+++ b/public/templates/internal_upload_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\timesheet-app\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EC4AA3-3184-4F03-A989-A03105AF82E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073E0031-487E-41B7-816F-B51A8DCB8EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{013FBE18-F61B-431E-9C57-53EF7E3B5338}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>Email</t>
   </si>
@@ -66,27 +66,12 @@
     <t>SubTeams</t>
   </si>
   <si>
-    <t>BA</t>
-  </si>
-  <si>
     <t>QA</t>
   </si>
   <si>
     <t>DEV</t>
   </si>
   <si>
-    <t>Bristol Bertha</t>
-  </si>
-  <si>
-    <t>Bbertha@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>rshaikh@slideinsurance.com</t>
-  </si>
-  <si>
-    <t>Rahil Shaikh</t>
-  </si>
-  <si>
     <t>Delivery/Scrum Master</t>
   </si>
   <si>
@@ -127,13 +112,19 @@
   </si>
   <si>
     <t>IT Ops</t>
+  </si>
+  <si>
+    <t>sjoginipalli@slideinsurance.com</t>
+  </si>
+  <si>
+    <t>Shravan Kumar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +146,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -184,11 +181,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -524,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5412F18-43F0-4B39-A3A8-2B1B8B345020}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" bestFit="1" customWidth="1"/>
@@ -547,38 +545,38 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -596,13 +594,13 @@
       <c r="A10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
+      <c r="A13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -613,17 +611,7 @@
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{03865FB7-B74E-4234-99FA-EE3ECEFDF54B}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{656875D4-773E-40C4-8E01-2F2BC43F934D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -668,7 +656,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -676,7 +664,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -684,7 +672,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -692,61 +680,61 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
